--- a/content/Meta/Programs/timeline_to_spreadsheet/output/timeline.xlsx
+++ b/content/Meta/Programs/timeline_to_spreadsheet/output/timeline.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="125">
   <si>
     <t>category</t>
   </si>
@@ -55,79 +55,145 @@
     <t>star_major</t>
   </si>
   <si>
+    <t>Encyclopedia Mysenvaria</t>
+  </si>
+  <si>
+    <t>Golden Age</t>
+  </si>
+  <si>
+    <t>Post-War Era</t>
+  </si>
+  <si>
+    <t>Iteration Period</t>
+  </si>
+  <si>
+    <t>Quickening</t>
+  </si>
+  <si>
+    <t>God Councils</t>
+  </si>
+  <si>
+    <t>Lover's Period</t>
+  </si>
+  <si>
+    <t>God-War Era</t>
+  </si>
+  <si>
     <t>Dying Period</t>
   </si>
   <si>
+    <t>The Great Poleward Fog Migration</t>
+  </si>
+  <si>
     <t>First Convening</t>
   </si>
   <si>
-    <t>First Death</t>
-  </si>
-  <si>
-    <t>God Councils</t>
-  </si>
-  <si>
     <t>Great Flood</t>
   </si>
   <si>
-    <t>Iteration Period</t>
-  </si>
-  <si>
-    <t>Quickening</t>
-  </si>
-  <si>
-    <t>Water Wars</t>
+    <t>Modern Era</t>
+  </si>
+  <si>
+    <t>Spatial Act</t>
   </si>
   <si>
     <t>Convening Star</t>
   </si>
   <si>
-    <t>The Dying Period begins following the First Death. It doesn't end until 160 BT, after the passing of three quarters of all Gods that have ever existed.</t>
-  </si>
-  <si>
-    <t>The Dying Period ends after the passing of three quarters of all Gods to ever exist. An estimated 11.2 billion Gods have passed away in seventeen years, over 1.9 million Gods per day.</t>
+    <t>Quickening Star</t>
+  </si>
+  <si>
+    <t>Encyclopedia Mysenvaria is published.</t>
+  </si>
+  <si>
+    <t>Start of the Golden Age. (end. 1214 AT)</t>
+  </si>
+  <si>
+    <t>End of the Golden Age. (beg. 609 AT)</t>
+  </si>
+  <si>
+    <t>Start of the Post-War Era. (end. 609 AT)</t>
+  </si>
+  <si>
+    <t>End of the Post-War Era. (beg. 0 AT)</t>
+  </si>
+  <si>
+    <t>The Iteration Period begins with the creation of the first organism by the God of Hydrogen Cyanide. It lasts until 55 BT and sees the creation of over 99% of all organisms to ever be created.</t>
+  </si>
+  <si>
+    <t>The Iteration Period ends following the passing of the Creations Act. 99% of all organisms which will ever exist were created since the start of the period.</t>
+  </si>
+  <si>
+    <t>The Quickening begins following the publication of the Quickening Star. An estimated 15 billion Gods are created over less than a single season.</t>
+  </si>
+  <si>
+    <t>First God Council held.</t>
+  </si>
+  <si>
+    <t>Second God Council held.</t>
+  </si>
+  <si>
+    <t>Third God Council held.</t>
+  </si>
+  <si>
+    <t>Fourth God Council held.</t>
+  </si>
+  <si>
+    <t>Fifth God Council held.</t>
+  </si>
+  <si>
+    <t>Sixth God Council held.</t>
+  </si>
+  <si>
+    <t>Start of the Lover's Period. (end. 12 BT)</t>
+  </si>
+  <si>
+    <t>End of the Lover's Period. (beg. 41 BT)</t>
+  </si>
+  <si>
+    <t>Start of the God-War Era. (end. 0 AT)</t>
+  </si>
+  <si>
+    <t>End of the God-War Era. (beg. 177 BT)</t>
+  </si>
+  <si>
+    <t>Start of the Early-War Epoch. (end. 116 BT)</t>
+  </si>
+  <si>
+    <t>End of the Early-War Epoch (beg. 116 BT), start of the Mid-War Epoch. (end. 55 BT)</t>
+  </si>
+  <si>
+    <t>End of the Mid-War Epoch (beg. 55 BT), start of the Late-War Epoch. (end. 0 AT)</t>
+  </si>
+  <si>
+    <t>The Dying Period begins (end. 160 BT) following the First Death. It doesn't end until 160 BT, after the passing of three quarters of all Gods that have ever existed.</t>
+  </si>
+  <si>
+    <t>The Dying Period ends (beg. 177 BT) after the passing of three quarters of all Gods which have ever existed. An estimated 11.2 billion Gods have passed away in seventeen years, over 1.9 million Gods per day.</t>
+  </si>
+  <si>
+    <t>Following the First God Council the Great Fog is shrunk drastically, to the scope known in the modern day. Millions of Gods are displaced and forced to migrate poleward, starting the Great Poleward Fog Migration.</t>
+  </si>
+  <si>
+    <t>The Great Poleward Fog Migration ends after a period of one season.</t>
   </si>
   <si>
     <t>The God of Fulgurite holds the First Convening. Of the 20 Gods invited only 16 arrive. Each invitee had witnessed the First Death. The event sees the formation of many ideas and theories regarding the beginning war.</t>
   </si>
   <si>
-    <t>As the number of Gods to ever exist reaches its peak the First Death of a God occurs.</t>
-  </si>
-  <si>
-    <t>First God Council held.</t>
-  </si>
-  <si>
-    <t>Second God Council held.</t>
-  </si>
-  <si>
-    <t>Third God Council held.</t>
-  </si>
-  <si>
-    <t>Fourth God Council held.</t>
-  </si>
-  <si>
-    <t>Fifth God Council held.</t>
-  </si>
-  <si>
-    <t>Sixth God Council held.</t>
-  </si>
-  <si>
-    <t>Start of the Great Flood.</t>
-  </si>
-  <si>
-    <t>End of the Great Flood.</t>
-  </si>
-  <si>
-    <t>The Iteration Period begins with the creation of the first organism by the God of Hydrogen Cyanide. It lasts until 55 BT and sees the creation of over 99% of all organisms to ever be created.</t>
-  </si>
-  <si>
-    <t>The Iteration Period ends following the passing of the Creations Act. 99% of all organisms which will ever exist were created since the start of the period.</t>
-  </si>
-  <si>
-    <t>The Quickening begins shortly after the first domain subdivisions by the Gods of What Is and Is Not. An estimated 15 billion Gods would be created over less than a single season.</t>
-  </si>
-  <si>
-    <t>On New Years the Great Water War takes place in the Oxygen-Hydrogen territories as Sodium, Calcium, Iron, and various allies attempt to stop the Great Flood.</t>
+    <t>Start of the Great Flood. (end. 11 BT)</t>
+  </si>
+  <si>
+    <t>End of the Great Flood. (beg. 25 BT)</t>
+  </si>
+  <si>
+    <t>Start of the Modern Era. (ongoing)</t>
+  </si>
+  <si>
+    <t>The modern day.</t>
+  </si>
+  <si>
+    <t>As Gods' manipulations of time and space grow more severe the Gods of Time and Space pass the Spatial Act.</t>
   </si>
   <si>
     <t>Following the First Convening the God of Fulgurite would publish the Convening Star, detailing the organizing of the event, the attendees, the discussions held, and the conclusions drawn.</t>
@@ -139,93 +205,129 @@
     <t>Following God of Sodium Ethyl Xanthate's own passing their close sibling God of Diethyl Dixanthogen Disulfide would republish many of their stars, including the Convening Star.</t>
   </si>
   <si>
+    <t>The God of Carbon publishes the Quickening Star to document their creation of the Carbon Compound Gods via domain subdivision. Other Elemental Gods follow behind, publishing their own stars and creating the Quickening System.</t>
+  </si>
+  <si>
+    <t>1313 AT</t>
+  </si>
+  <si>
+    <t>609 AT</t>
+  </si>
+  <si>
+    <t>1214 AT</t>
+  </si>
+  <si>
+    <t>0 AT</t>
+  </si>
+  <si>
+    <t>140 BT</t>
+  </si>
+  <si>
+    <t>55 BT</t>
+  </si>
+  <si>
+    <t>294th of 178 BT</t>
+  </si>
+  <si>
+    <t>1st of 145 BT</t>
+  </si>
+  <si>
+    <t>1st of 55 BT</t>
+  </si>
+  <si>
+    <t>1st of 39 BT</t>
+  </si>
+  <si>
+    <t>1st of 12 BT</t>
+  </si>
+  <si>
+    <t>1st of 6 BT</t>
+  </si>
+  <si>
+    <t>360th of 1 BT</t>
+  </si>
+  <si>
+    <t>41 BT</t>
+  </si>
+  <si>
+    <t>12 BT</t>
+  </si>
+  <si>
+    <t>177 BT</t>
+  </si>
+  <si>
+    <t>116 BT</t>
+  </si>
+  <si>
     <t>26th of 177 BT</t>
   </si>
   <si>
     <t>267th of 160 BT</t>
   </si>
   <si>
+    <t>90th of 145 BT</t>
+  </si>
+  <si>
     <t>176 BT</t>
   </si>
   <si>
-    <t>145 BT</t>
-  </si>
-  <si>
-    <t>55 BT</t>
-  </si>
-  <si>
-    <t>39 BT</t>
-  </si>
-  <si>
-    <t>12 BT</t>
+    <t>25 BT</t>
+  </si>
+  <si>
+    <t>11 BT</t>
+  </si>
+  <si>
+    <t>1496 AT</t>
+  </si>
+  <si>
+    <t>213th of 175 BT</t>
+  </si>
+  <si>
+    <t>53 BT</t>
+  </si>
+  <si>
+    <t>1 BT</t>
+  </si>
+  <si>
+    <t>Gods of Time and Space</t>
+  </si>
+  <si>
+    <t>God of Fulgurite</t>
+  </si>
+  <si>
+    <t>God of Sodium Ethyl Xanthate</t>
+  </si>
+  <si>
+    <t>God of Diethyl Dixanthogen Disulfide</t>
+  </si>
+  <si>
+    <t>God of Carbon</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>major_event</t>
+  </si>
+  <si>
+    <t>death</t>
+  </si>
+  <si>
+    <t>Charles Lightningson</t>
+  </si>
+  <si>
+    <t>Encyclopedia Mysenvaria/History/Biographies/Charles Lightningson.md</t>
   </si>
   <si>
     <t>6 BT</t>
   </si>
   <si>
-    <t>0 AT</t>
-  </si>
-  <si>
-    <t>25 BT</t>
-  </si>
-  <si>
-    <t>11 BT</t>
-  </si>
-  <si>
-    <t>140 BT</t>
-  </si>
-  <si>
-    <t>294th of 178 BT</t>
-  </si>
-  <si>
-    <t>1st of 25 BT</t>
-  </si>
-  <si>
-    <t>53 BT</t>
-  </si>
-  <si>
-    <t>1 BT</t>
-  </si>
-  <si>
-    <t>God of Fulgurite</t>
-  </si>
-  <si>
-    <t>God of Sodium Ethyl Xanthate</t>
-  </si>
-  <si>
-    <t>God of Diethyl Dixanthogen Disulfide</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>major_event</t>
-  </si>
-  <si>
-    <t>birth</t>
-  </si>
-  <si>
-    <t>death</t>
-  </si>
-  <si>
-    <t>Josh Soundson</t>
-  </si>
-  <si>
-    <t>Charles Lightningson</t>
-  </si>
-  <si>
-    <t>Encyclopedia Mysenvaria/History/Biographies/Josh Soundson.md</t>
-  </si>
-  <si>
-    <t>Encyclopedia Mysenvaria/History/Biographies/Charles Lightningson.md</t>
-  </si>
-  <si>
     <t>first_pub_year</t>
   </si>
   <si>
@@ -247,10 +349,19 @@
     <t>282nd of 178 BT</t>
   </si>
   <si>
-    <t>The oldest star, created by the Gods of What Is and Is Not to document their creation of the Plane and the first other Gods, the Gods of Matter, Energy, Time, and Space.</t>
+    <t>0.0,0.0,3844.0</t>
+  </si>
+  <si>
+    <t>The oldest star, created by the Gods of What Is and Is Not to document their creation of the Plane and the Creation Quadrinity.</t>
+  </si>
+  <si>
+    <t>The host star of the Quickening System. Created by the God of Carbon to document their creation of the Carbon Compound Gods.</t>
   </si>
   <si>
     <t>Published by the God of Fulgurite following the First Convening. It details the organizing of the event, the attendees, the discussions held, and the conclusions drawn.</t>
+  </si>
+  <si>
+    <t>Published by the Gods of Time and Space to put an end to Gods' manipulation of time and space as battle strategies.</t>
   </si>
   <si>
     <t>Gods of What Is and Is Not</t>
@@ -638,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -678,53 +789,47 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>-177</v>
-      </c>
-      <c r="E2">
-        <v>26</v>
+        <v>1313</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>-160</v>
-      </c>
-      <c r="E3">
-        <v>267</v>
+        <v>609</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>-176</v>
+        <v>1214</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -735,33 +840,30 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>-177</v>
-      </c>
-      <c r="E5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>-145</v>
+        <v>609</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -772,30 +874,30 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>-55</v>
+        <v>-140</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D8">
-        <v>-39</v>
+        <v>-55</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -803,16 +905,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>-12</v>
+        <v>-178</v>
+      </c>
+      <c r="E9">
+        <v>294</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -820,16 +925,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-145</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -837,16 +945,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>-55</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -854,33 +965,39 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D12">
-        <v>-25</v>
+        <v>-39</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D13">
-        <v>-11</v>
+        <v>-12</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -891,30 +1008,36 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>-140</v>
+        <v>-6</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D15">
-        <v>-55</v>
+        <v>-1</v>
+      </c>
+      <c r="E15">
+        <v>360</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -925,105 +1048,401 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D16">
-        <v>-178</v>
-      </c>
-      <c r="E16">
-        <v>294</v>
+        <v>-41</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D17">
-        <v>-25</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D18">
-        <v>-176</v>
+        <v>-177</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D19">
-        <v>-53</v>
+        <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20">
+        <v>-177</v>
+      </c>
+      <c r="F20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>-116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22">
+        <v>-55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>-177</v>
+      </c>
+      <c r="E23">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>-160</v>
+      </c>
+      <c r="E24">
+        <v>267</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>-145</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26">
+        <v>-145</v>
+      </c>
+      <c r="E26">
+        <v>90</v>
+      </c>
+      <c r="F26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27">
+        <v>-176</v>
+      </c>
+      <c r="F27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28">
+        <v>-25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29">
+        <v>-11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30">
+        <v>1214</v>
+      </c>
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31">
+        <v>1496</v>
+      </c>
+      <c r="F31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
         <v>11</v>
       </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32">
+        <v>-175</v>
+      </c>
+      <c r="E32">
+        <v>213</v>
+      </c>
+      <c r="F32" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33">
+        <v>-176</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34">
+        <v>-53</v>
+      </c>
+      <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35">
         <v>-1</v>
       </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s">
-        <v>58</v>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36">
+        <v>-178</v>
+      </c>
+      <c r="E36">
+        <v>294</v>
+      </c>
+      <c r="F36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1033,18 +1452,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -1059,75 +1478,29 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3">
-        <v>-12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4">
-        <v>-6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1138,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1149,30 +1522,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="C2">
         <v>-178</v>
@@ -1181,33 +1554,82 @@
         <v>282</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>110</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C3">
+        <v>-178</v>
+      </c>
+      <c r="D3">
+        <v>294</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
         <v>-176</v>
       </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" t="s">
-        <v>56</v>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>-175</v>
+      </c>
+      <c r="D5">
+        <v>213</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1222,13 +1644,13 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1240,24 +1662,24 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="D2">
         <v>-42</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="G2">
         <v>-12</v>
@@ -1265,19 +1687,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="D3">
         <v>-12</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G3">
         <v>-42</v>
